--- a/library/ai-mini-drama/ios/cases.xlsx
+++ b/library/ai-mini-drama/ios/cases.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2860" uniqueCount="1718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2924" uniqueCount="1761">
   <si>
     <t>ID</t>
   </si>
@@ -1796,19 +1796,19 @@
     <t>Credits and limits</t>
   </si>
   <si>
-    <t>Account still has free creations</t>
-  </si>
-  <si>
-    <t>Look at an action card</t>
-  </si>
-  <si>
-    <t>「Free for your first 3 creations - {n} left.」</t>
-  </si>
-  <si>
-    <t>R-099</t>
-  </si>
-  <si>
-    <t>Account already used its free creations → Blocked</t>
+    <t>Account still has free storyboard tries</t>
+  </si>
+  <si>
+    <t>Look at the 「Create storyboard」 card; create one storyboard, then look at the next card</t>
+  </si>
+  <si>
+    <t>The price ◆15 is struck through with 「Free • {n} left」, {n} = tries left; the next card shows one fewer</t>
+  </si>
+  <si>
+    <t>R-099, R-259</t>
+  </si>
+  <si>
+    <t>Design 1016_support free trial (Figma 4847:34277), newer than the MX-board frame 「Free for your first 3 creations - {n} left.」; PM says nothing different (REQ-029). Needs an account with free tries → Blocked</t>
   </si>
   <si>
     <t>TC-115</t>
@@ -5114,6 +5114,135 @@
     <t>PM E4 frame; where the button leads is not drawn. The failure copy is checked in TC-078</t>
   </si>
   <si>
+    <t>TC-356</t>
+  </si>
+  <si>
+    <t>Free storyboard tries used up (the shared test account)</t>
+  </si>
+  <si>
+    <t>Look at the 「Create storyboard」 card</t>
+  </si>
+  <si>
+    <t>Only the price shows (e.g. ◆15): no strikethrough and no 「Free」</t>
+  </si>
+  <si>
+    <t>R-260</t>
+  </si>
+  <si>
+    <t>Design 1016_support free trial (Figma 4847:34277)</t>
+  </si>
+  <si>
+    <t>TC-357</t>
+  </si>
+  <si>
+    <t>Tap New chat, then 「Stay」; tap the credit pill, then 「Stay」</t>
+  </si>
+  <si>
+    <t>Each tap shows 「Leave this chat?」/「Your story outline isn't ready yet, so this chat won't be saved.」 with Leave anyway / Stay; Stay closes it, the chat stays and the outline still arrives</t>
+  </si>
+  <si>
+    <t>R-261</t>
+  </si>
+  <si>
+    <t>Exits from Design 1016_Chat navigation; dialog copy from PM 10/21, which is newer (REQ-029). TC-025 – TC-028 cover Back and History</t>
+  </si>
+  <si>
+    <t>TC-358</t>
+  </si>
+  <si>
+    <t>Outline generating for a new idea</t>
+  </si>
+  <si>
+    <t>Tap the credit pill, then 「Leave anyway」; then open History</t>
+  </si>
+  <si>
+    <t>My Credits opens; History has no entry for this idea</t>
+  </si>
+  <si>
+    <t>Landing page from Design 1016_Chat navigation (REQ-029)</t>
+  </si>
+  <si>
+    <t>TC-359</t>
+  </si>
+  <si>
+    <t>Tap History, then 「Keep Generating」; tap New chat, then 「Keep Generating」; tap the credit pill, then 「Leave anyway」</t>
+  </si>
+  <si>
+    <t>Each tap shows 「Stop and lose your credits?」/「This is still generating. If you leave now, it'll stop and the credits you've spent won't be refunded.」 with Leave anyway / Keep Generating; Keep Generating keeps it running; Leave anyway stops it and opens My Credits</t>
+  </si>
+  <si>
+    <t>R-262</t>
+  </si>
+  <si>
+    <t>PM 10/21 §13.6 governs the dialog; Design 1016 shows 「Leave this chat?」 but is older (REQ-029). TC-061 covers Back</t>
+  </si>
+  <si>
+    <t>TC-360</t>
+  </si>
+  <si>
+    <t>Outline finished, nothing generating</t>
+  </si>
+  <si>
+    <t>Tap History; reopen the drama; tap the credit pill; go back; tap New chat</t>
+  </si>
+  <si>
+    <t>No dialog each time; History opens Recent Task with this drama listed, the credit pill opens My Credits, New chat opens a new empty chat</t>
+  </si>
+  <si>
+    <t>R-263</t>
+  </si>
+  <si>
+    <t>PM: saved chats leave with no dialog; Design 1016 shows 「Leave this chat?」 but is older (REQ-029). TC-029 covers Back</t>
+  </si>
+  <si>
+    <t>TC-361</t>
+  </si>
+  <si>
+    <t>No dialog each time; 「We'll keep making your video. Find it in History.」 shows on leaving; Recent Task, My Credits and a new empty chat open in turn; the video keeps generating</t>
+  </si>
+  <si>
+    <t>R-264</t>
+  </si>
+  <si>
+    <t>PM governs; Design 1016 shows 「Leave this chat?」 but is older (REQ-029). TC-082 covers Back</t>
+  </si>
+  <si>
+    <t>TC-362</t>
+  </si>
+  <si>
+    <t>One scene video fails with 4xxx (Pink › Inject failure status = moderation_blocked, that beat; record the switch)</t>
+  </si>
+  <si>
+    <t>Look at the failed clip, then tap ⓘ</t>
+  </si>
+  <si>
+    <t>The clip card shows 「Couldn't create video ⓘ」 with the refund text; ⓘ opens 「Couldn't generate this video」/「Your credits have been refunded. The description may not meet our terms of service, such as violence, NSFW content, or content involving minors. Edit the description to try again.」 with Got it</t>
+  </si>
+  <si>
+    <t>R-257</t>
+  </si>
+  <si>
+    <t>PM error board, 10/13 update. Card text: the §13.7 copy table gives 「Couldn't create video. The description may not meet our terms of service. Your credits have been refunded. Edit the description and try again.」; record which one shows</t>
+  </si>
+  <si>
+    <t>TC-363</t>
+  </si>
+  <si>
+    <t>One scene video fails with 5xxx (Pink › Inject failure status = tool_error, that beat; record the switch)</t>
+  </si>
+  <si>
+    <t>Look at the failed clip and tap where ⓘ would be</t>
+  </si>
+  <si>
+    <t>The clip card shows 「Couldn't create video」 with the refund text and no ⓘ; no dialog opens</t>
+  </si>
+  <si>
+    <t>R-258</t>
+  </si>
+  <si>
+    <t>PM error board, 10/13 update (5xxx cards drop the ⓘ). §13.7 card text: 「Couldn't create video. Our service is busy right now. Your credits have been refunded. Try again later.」</t>
+  </si>
+  <si>
     <t>Feature</t>
   </si>
   <si>
@@ -5135,19 +5264,19 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4</t>
+    <t>6</t>
   </si>
   <si>
     <t>Approved</t>
   </si>
   <si>
-    <t>2026-10-22T01:18:30.999Z</t>
+    <t>2026-10-22T03:39:31.188Z</t>
   </si>
   <si>
     <t>Cases</t>
   </si>
   <si>
-    <t>354</t>
+    <t>362</t>
   </si>
   <si>
     <t>Spec set SHA-256</t>
@@ -5562,7 +5691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H355"/>
+  <dimension ref="A1:H363"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -14801,6 +14930,214 @@
       </c>
       <c r="H355" s="3" t="s">
         <v>1699</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A356" s="3" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B356" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C356" s="3" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D356" s="3" t="s">
+        <v>1702</v>
+      </c>
+      <c r="E356" s="3" t="s">
+        <v>1703</v>
+      </c>
+      <c r="F356" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G356" s="3" t="s">
+        <v>1704</v>
+      </c>
+      <c r="H356" s="3" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A357" s="3" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B357" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C357" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D357" s="3" t="s">
+        <v>1707</v>
+      </c>
+      <c r="E357" s="3" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F357" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G357" s="3" t="s">
+        <v>1709</v>
+      </c>
+      <c r="H357" s="3" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A358" s="3" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B358" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C358" s="3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D358" s="3" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E358" s="3" t="s">
+        <v>1714</v>
+      </c>
+      <c r="F358" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G358" s="3" t="s">
+        <v>1709</v>
+      </c>
+      <c r="H358" s="3" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A359" s="3" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B359" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C359" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D359" s="3" t="s">
+        <v>1717</v>
+      </c>
+      <c r="E359" s="3" t="s">
+        <v>1718</v>
+      </c>
+      <c r="F359" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G359" s="3" t="s">
+        <v>1719</v>
+      </c>
+      <c r="H359" s="3" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A360" s="3" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B360" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C360" s="3" t="s">
+        <v>1722</v>
+      </c>
+      <c r="D360" s="3" t="s">
+        <v>1723</v>
+      </c>
+      <c r="E360" s="3" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F360" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G360" s="3" t="s">
+        <v>1725</v>
+      </c>
+      <c r="H360" s="3" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A361" s="3" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B361" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C361" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="D361" s="3" t="s">
+        <v>1723</v>
+      </c>
+      <c r="E361" s="3" t="s">
+        <v>1728</v>
+      </c>
+      <c r="F361" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G361" s="3" t="s">
+        <v>1729</v>
+      </c>
+      <c r="H361" s="3" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A362" s="3" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B362" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C362" s="3" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D362" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="E362" s="3" t="s">
+        <v>1734</v>
+      </c>
+      <c r="F362" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G362" s="3" t="s">
+        <v>1735</v>
+      </c>
+      <c r="H362" s="3" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A363" s="3" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B363" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C363" s="3" t="s">
+        <v>1738</v>
+      </c>
+      <c r="D363" s="3" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E363" s="3" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F363" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G363" s="3" t="s">
+        <v>1741</v>
+      </c>
+      <c r="H363" s="3" t="s">
+        <v>1742</v>
       </c>
     </row>
   </sheetData>
@@ -14821,82 +15158,82 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1700</v>
+        <v>1743</v>
       </c>
       <c r="B1" t="s">
-        <v>1701</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>1702</v>
+        <v>1745</v>
       </c>
       <c r="B2" t="s">
-        <v>1703</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>1704</v>
+        <v>1747</v>
       </c>
       <c r="B3" t="s">
-        <v>1705</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1706</v>
+        <v>1749</v>
       </c>
       <c r="B4" t="s">
-        <v>1707</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>1708</v>
+        <v>1751</v>
       </c>
       <c r="B5" t="s">
-        <v>1709</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>1710</v>
+        <v>1753</v>
       </c>
       <c r="B6" t="s">
-        <v>1711</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>1712</v>
+        <v>1755</v>
       </c>
       <c r="B7" t="s">
-        <v>1713</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>1714</v>
+        <v>1757</v>
       </c>
       <c r="B8" t="s">
-        <v>1715</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>1714</v>
+        <v>1757</v>
       </c>
       <c r="B9" t="s">
-        <v>1716</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>1714</v>
+        <v>1757</v>
       </c>
       <c r="B10" t="s">
-        <v>1717</v>
+        <v>1760</v>
       </c>
     </row>
   </sheetData>

--- a/library/ai-mini-drama/ios/cases.xlsx
+++ b/library/ai-mini-drama/ios/cases.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2924" uniqueCount="1761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2972" uniqueCount="1791">
   <si>
     <t>ID</t>
   </si>
@@ -5243,6 +5243,96 @@
     <t>PM error board, 10/13 update (5xxx cards drop the ⓘ). §13.7 card text: 「Couldn't create video. Our service is busy right now. Your credits have been refunded. Try again later.」</t>
   </si>
   <si>
+    <t>TC-364</t>
+  </si>
+  <si>
+    <t>Drama created with 「No captions」; Log stage timings ON</t>
+  </si>
+  <si>
+    <t>Generate the full video; when it finishes, pull the logs and read this video's tool calls</t>
+  </si>
+  <si>
+    <t>The video has no captions, and the log shows no speech-to-text (STT) call for it</t>
+  </si>
+  <si>
+    <t>PM §13.13 (10/6): 「user 選 No captions 時不跑STT」. TC-097 checks the video; this row checks STT did not run. If no log line marks STT on a captioned video either, record Blocked (observability) and ask RD which line does. Spec agent 1012-PM-CAPTIONS-NO-STT (REQ-031)</t>
+  </si>
+  <si>
+    <t>TC-365</t>
+  </si>
+  <si>
+    <t>Captions failed on some segments only (「Captions couldn't be added. Try again」); Log stage timings ON</t>
+  </si>
+  <si>
+    <t>Tap Try again; when the captions appear, pull the logs and compare the STT calls before and after the retry</t>
+  </si>
+  <si>
+    <t>The retry sends only the segments that failed to STT again; the captions appear all at once when every segment has succeeded</t>
+  </si>
+  <si>
+    <t>PM §13.13 (10/6): 「只重跑失敗的段落，全部成功才把字幕一次放上去」. No fault switch makes STT fail (TC-298) → Blocked (observability) until RD gives a fixture. Spec agent 1012-PM-CAPTION-RETRY-SEGMENTS (REQ-031)</t>
+  </si>
+  <si>
+    <t>TC-366</t>
+  </si>
+  <si>
+    <t>Make your character open; a reference photo with an easily recognized object near one edge</t>
+  </si>
+  <si>
+    <t>Add the photo, crop the edge object away in Crop and tap ✓, then Generate; afterwards pull the logs and open the stored reference image (ai-mini-drama-reference-photos)</t>
+  </si>
+  <si>
+    <t>The reference image used for the character shows only the cropped area: the cropped-away object is not in it</t>
+  </si>
+  <si>
+    <t>R-265</t>
+  </si>
+  <si>
+    <t>PM main flow note 「只送 crop 後的圖」 (missed by the first reading; confirmed by a render 2026-10-22). If the pulled logs hold no reference image, record Blocked (observability) and ask RD for the uploaded image. Spec agent 1012-PM-CROP-UPLOAD (REQ-031)</t>
+  </si>
+  <si>
+    <t>TC-367</t>
+  </si>
+  <si>
+    <t>Tier Pro (Pink › IAP › Status › Pro); remaining chats known (finite allowance)</t>
+  </si>
+  <si>
+    <t>Each of the three uses exactly one of the Pro daily chats (allowance 30)</t>
+  </si>
+  <si>
+    <t>MX ① version A. TC-218 runs the same check on any tier; each tier gets its own row (REQ-031). 9999 Developer Server limit → Blocked (chat-count). Spec agent MX-PRO-SEND-DEBIT-001 (REQ-031)</t>
+  </si>
+  <si>
+    <t>TC-368</t>
+  </si>
+  <si>
+    <t>Tier Pro+ (Pink › IAP › Status › Pro+); remaining chats known (finite allowance)</t>
+  </si>
+  <si>
+    <t>Each of the three uses exactly one of the Pro+ daily chats (allowance 100)</t>
+  </si>
+  <si>
+    <t>MX ① version A. TC-218 runs the same check on any tier; each tier gets its own row (REQ-031). 9999 Developer Server limit → Blocked (chat-count). Spec agent MX-PROPLUS-SEND-DEBIT-001 (REQ-031)</t>
+  </si>
+  <si>
+    <t>TC-369</t>
+  </si>
+  <si>
+    <t>RD has changed the Firebase Remote Config daily chat allowance for the tier under test (e.g. Free → 3); app relaunched</t>
+  </si>
+  <si>
+    <t>Send chats until the limit dialog appears, counting each send</t>
+  </si>
+  <si>
+    <t>The limit dialog appears on the send after the new allowance (the 4th for 3), not at the spec default (11th)</t>
+  </si>
+  <si>
+    <t>R-266</t>
+  </si>
+  <si>
+    <t>MX ① version A: allowance is remote-configured (Firebase). The spec does not say when a change takes effect, so relaunch first. Needs RD to change Remote Config → Blocked (remote-config). Spec agent FIXTURE-0924-S002-B016 (REQ-031)</t>
+  </si>
+  <si>
     <t>Feature</t>
   </si>
   <si>
@@ -5264,19 +5354,19 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6</t>
+    <t>7</t>
   </si>
   <si>
     <t>Approved</t>
   </si>
   <si>
-    <t>2026-10-22T03:39:31.188Z</t>
+    <t>2026-10-22T06:29:41.325Z</t>
   </si>
   <si>
     <t>Cases</t>
   </si>
   <si>
-    <t>362</t>
+    <t>368</t>
   </si>
   <si>
     <t>Spec set SHA-256</t>
@@ -5691,7 +5781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H363"/>
+  <dimension ref="A1:H369"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -15138,6 +15228,162 @@
       </c>
       <c r="H363" s="3" t="s">
         <v>1742</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A364" s="3" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B364" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C364" s="3" t="s">
+        <v>1744</v>
+      </c>
+      <c r="D364" s="3" t="s">
+        <v>1745</v>
+      </c>
+      <c r="E364" s="3" t="s">
+        <v>1746</v>
+      </c>
+      <c r="F364" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G364" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="H364" s="3" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A365" s="3" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B365" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C365" s="3" t="s">
+        <v>1749</v>
+      </c>
+      <c r="D365" s="3" t="s">
+        <v>1750</v>
+      </c>
+      <c r="E365" s="3" t="s">
+        <v>1751</v>
+      </c>
+      <c r="F365" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G365" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="H365" s="3" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A366" s="3" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B366" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C366" s="3" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D366" s="3" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E366" s="3" t="s">
+        <v>1756</v>
+      </c>
+      <c r="F366" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G366" s="3" t="s">
+        <v>1757</v>
+      </c>
+      <c r="H366" s="3" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A367" s="3" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B367" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C367" s="3" t="s">
+        <v>1760</v>
+      </c>
+      <c r="D367" s="3" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E367" s="3" t="s">
+        <v>1761</v>
+      </c>
+      <c r="F367" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G367" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H367" s="3" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A368" s="3" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B368" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C368" s="3" t="s">
+        <v>1764</v>
+      </c>
+      <c r="D368" s="3" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E368" s="3" t="s">
+        <v>1765</v>
+      </c>
+      <c r="F368" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G368" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H368" s="3" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A369" s="3" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B369" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C369" s="3" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D369" s="3" t="s">
+        <v>1769</v>
+      </c>
+      <c r="E369" s="3" t="s">
+        <v>1770</v>
+      </c>
+      <c r="F369" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G369" s="3" t="s">
+        <v>1771</v>
+      </c>
+      <c r="H369" s="3" t="s">
+        <v>1772</v>
       </c>
     </row>
   </sheetData>
@@ -15158,82 +15404,82 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1743</v>
+        <v>1773</v>
       </c>
       <c r="B1" t="s">
-        <v>1744</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>1745</v>
+        <v>1775</v>
       </c>
       <c r="B2" t="s">
-        <v>1746</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>1747</v>
+        <v>1777</v>
       </c>
       <c r="B3" t="s">
-        <v>1748</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1749</v>
+        <v>1779</v>
       </c>
       <c r="B4" t="s">
-        <v>1750</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>1751</v>
+        <v>1781</v>
       </c>
       <c r="B5" t="s">
-        <v>1752</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>1753</v>
+        <v>1783</v>
       </c>
       <c r="B6" t="s">
-        <v>1754</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>1755</v>
+        <v>1785</v>
       </c>
       <c r="B7" t="s">
-        <v>1756</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>1757</v>
+        <v>1787</v>
       </c>
       <c r="B8" t="s">
-        <v>1758</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>1757</v>
+        <v>1787</v>
       </c>
       <c r="B9" t="s">
-        <v>1759</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>1757</v>
+        <v>1787</v>
       </c>
       <c r="B10" t="s">
-        <v>1760</v>
+        <v>1790</v>
       </c>
     </row>
   </sheetData>

--- a/library/ai-mini-drama/ios/cases.xlsx
+++ b/library/ai-mini-drama/ios/cases.xlsx
@@ -1436,10 +1436,10 @@
     <t>TC-389</t>
   </si>
   <si>
-    <t>Storyboard generating; a scene with a Location</t>
-  </si>
-  <si>
-    <t>Open that scene's detail while it generates and watch the Location thumbnail</t>
+    <t>Scene detail (Scene edit page) open while that scene's Location image is still generating: the scene regenerated from Edit (TC-070) or updated through Iris (TC-073)</t>
+  </si>
+  <si>
+    <t>Watch the Location thumbnail under the main image until both images finish</t>
   </si>
   <si>
     <t>The Location thumbnail shows a skeleton, then the location image before the main image finishes; the main image keeps its width</t>
@@ -1448,7 +1448,7 @@
     <t>R-299</t>
   </si>
   <si>
-    <t>PM 10/14 board 6; TC-066 notes the Design draws no 「Location」 label</t>
+    <t>PM 10/14 board 6 「10/12 update - Scene 編輯頁的「地點圖片」」: the rule is for the Scene edit page only. The chat storyboard card shows one skeleton loader (Design) and is not this row; if no scene detail can be opened while its Location generates, record Blocked (test-data), not a finding on another screen (Android DRA262610P0345 was filed from that misreading; PDRA 2026-10-29, REQ-055). TC-066 notes the Design draws no 「Location」 label</t>
   </si>
   <si>
     <t>TC-390</t>
